--- a/AAII_Financials/Yearly/UWMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UWMC_YR_FIN.xlsx
@@ -1908,13 +1908,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>503400</v>
+        <v>482400</v>
       </c>
       <c r="E41" s="3">
-        <v>507300</v>
+        <v>491300</v>
       </c>
       <c r="F41" s="3">
-        <v>497500</v>
+        <v>496500</v>
       </c>
       <c r="G41" s="3">
         <v>704900</v>
